--- a/config.xlsx
+++ b/config.xlsx
@@ -1,37 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\03_Test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078DF45F-AD48-4EDB-A311-46677F1A4304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="9756" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Config" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>Anzeigename</t>
+  </si>
+  <si>
+    <t>Dateiname</t>
+  </si>
+  <si>
+    <t>vocabolario.xlsx</t>
+  </si>
+  <si>
+    <t>VocabolarIo</t>
+  </si>
+  <si>
+    <t>VocabolarIo Test</t>
+  </si>
+  <si>
+    <t>vocabolario_test.xlsx</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,81 +79,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,64 +382,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Anzeigename</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Dateiname</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Verben A1/A2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>verben.xlsx</t>
-        </is>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Körperteile</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>koerperteile.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Kalender</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>kalender.xlsx</t>
-        </is>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\03_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078DF45F-AD48-4EDB-A311-46677F1A4304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA91F3D-FFAB-437F-98CA-C3C6AA280F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="9756" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="9756" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Anzeigename</t>
   </si>
@@ -31,13 +31,7 @@
     <t>vocabolario.xlsx</t>
   </si>
   <si>
-    <t>VocabolarIo</t>
-  </si>
-  <si>
-    <t>VocabolarIo Test</t>
-  </si>
-  <si>
-    <t>vocabolario_test.xlsx</t>
+    <t>VocabolarIo A1-A2</t>
   </si>
 </sst>
 </file>
@@ -383,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -406,14 +400,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\03_Test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Christian Beck\VocabolarIo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA91F3D-FFAB-437F-98CA-C3C6AA280F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5886E3-ED8C-4E7F-9924-8A8A863E7A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3036" yWindow="3036" windowWidth="9756" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Anzeigename</t>
   </si>
@@ -28,10 +28,16 @@
     <t>Dateiname</t>
   </si>
   <si>
-    <t>vocabolario.xlsx</t>
-  </si>
-  <si>
-    <t>VocabolarIo A1-A2</t>
+    <t>VocabolarIo</t>
+  </si>
+  <si>
+    <t>Artikel</t>
+  </si>
+  <si>
+    <t>vocabolario_V1.xlsx</t>
+  </si>
+  <si>
+    <t>artikel_V1.xlsx</t>
   </si>
 </sst>
 </file>
@@ -377,14 +383,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,12 +398,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Christian Beck\VocabolarIo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\03_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5886E3-ED8C-4E7F-9924-8A8A863E7A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545B3066-D524-44E2-874D-99126AEC8AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -31,10 +31,10 @@
     <t>VocabolarIo</t>
   </si>
   <si>
+    <t>vocabolario_V2.1.xlsx</t>
+  </si>
+  <si>
     <t>Artikel</t>
-  </si>
-  <si>
-    <t>vocabolario_V1.xlsx</t>
   </si>
   <si>
     <t>artikel_V1.xlsx</t>
@@ -78,9 +78,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -384,13 +385,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -398,19 +399,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\03_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545B3066-D524-44E2-874D-99126AEC8AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BED860-3957-424D-96E3-531F5179B62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,10 +34,10 @@
     <t>vocabolario_V2.1.xlsx</t>
   </si>
   <si>
-    <t>Artikel</t>
-  </si>
-  <si>
-    <t>artikel_V1.xlsx</t>
+    <t>Grammatica</t>
+  </si>
+  <si>
+    <t>grammatica_V2.0.xlsx</t>
   </si>
 </sst>
 </file>
@@ -78,10 +78,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -408,10 +407,10 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\03_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BED860-3957-424D-96E3-531F5179B62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC5B719-1548-4975-B25D-2CE5FDCE1215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Anzeigename</t>
   </si>
@@ -38,6 +38,12 @@
   </si>
   <si>
     <t>grammatica_V2.0.xlsx</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>test.xlsx</t>
   </si>
 </sst>
 </file>
@@ -383,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -414,6 +420,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\03_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC5B719-1548-4975-B25D-2CE5FDCE1215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD4946E-8ED5-48DA-96CE-08D1097E5D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="1440" windowWidth="27000" windowHeight="14040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
     <t>VocabolarIo</t>
   </si>
   <si>
-    <t>vocabolario_V2.1.xlsx</t>
-  </si>
-  <si>
     <t>Grammatica</t>
   </si>
   <si>
@@ -44,6 +41,9 @@
   </si>
   <si>
     <t>test.xlsx</t>
+  </si>
+  <si>
+    <t>vocabolario_V2.2.xlsx</t>
   </si>
 </sst>
 </file>
@@ -409,23 +409,23 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\03_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD4946E-8ED5-48DA-96CE-08D1097E5D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25F6ECD-E0CD-4582-9F7B-AD74C6573AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="1440" windowWidth="27000" windowHeight="14040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Anzeigename</t>
   </si>
@@ -31,19 +31,7 @@
     <t>VocabolarIo</t>
   </si>
   <si>
-    <t>Grammatica</t>
-  </si>
-  <si>
-    <t>grammatica_V2.0.xlsx</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>test.xlsx</t>
-  </si>
-  <si>
-    <t>vocabolario_V2.2.xlsx</t>
+    <t>vocabolario_V2.4.xlsx</t>
   </si>
 </sst>
 </file>
@@ -389,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -409,23 +397,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
